--- a/bot/orders/120863478.xlsx
+++ b/bot/orders/120863478.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>16.00</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>17.00</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>18.00</t>
         </is>
       </c>
     </row>
